--- a/src/main/r/rws/projs/inventory/data/companies.xlsx
+++ b/src/main/r/rws/projs/inventory/data/companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\main\r\rws\projs\inventory\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877E8557-1BBA-4E26-8642-87306E82ED00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21D9B1D-E102-43A8-80D5-8393DAFCE921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="467">
   <si>
     <t>中文名</t>
   </si>
@@ -1433,10 +1433,6 @@
   </si>
   <si>
     <t>description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1790,7 +1786,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>453</v>
@@ -1811,7 +1807,7 @@
         <v>457</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>456</v>
@@ -3490,18 +3486,6 @@
       </c>
       <c r="J39" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
   </sheetData>
